--- a/docs/data/jp/xlsx/9216.xlsx
+++ b/docs/data/jp/xlsx/9216.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -762,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC193"/>
+  <dimension ref="A1:AC200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4274,11 +4277,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>1653</v>
+        <v>1636</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5515,7 +5518,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5767,402 +5770,529 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>8094.089</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>7889.266</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>8059.288</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>7756</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>7875</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>7652</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>7953</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>7791</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>7668</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>7625</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>7880</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>7906</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>7073.522</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>7976.884</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>8059.288</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>7953</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>7880</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>1594.986</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>1492.651</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>1472.504</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>1336</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>1422</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>1164</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>1139</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>1341</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1354</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>1524</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>1505</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>1280.457</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>1494.389</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>1472.504</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>1265</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>1524</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>837.191</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>866.698</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>959.136</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>953</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>950</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>938</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>1276</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>1005</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>947</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>905</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>1334</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>1025</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>797.853</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>773.228</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>959.136</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>1276</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>1334</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>757.795</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>625.953</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>513.3680000000001</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>382</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>473</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>225</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>-11</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>393</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>449</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>191</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>479</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>482.604</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>721.1609999999999</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>513.3680000000001</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>-11</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>191</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0</v>
+        <v>837.191</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0</v>
+        <v>866.698</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0.001</v>
+        <v>959.136</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>0</v>
+        <v>1276</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>0</v>
+        <v>1334</v>
+      </c>
+      <c r="N83" s="22" t="n">
+        <v>1025</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>0.001</v>
+        <v>797.853</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0.001</v>
+        <v>773.228</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.001</v>
+        <v>959.136</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>0</v>
+        <v>1276</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>0</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>757.795</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>625.953</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>513.3680000000001</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>382</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>473</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>-11</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>393</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>449</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>479</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>482.604</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>721.1609999999999</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>513.3680000000001</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>-11</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>보험금 수익</t>
-        </is>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>1</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>3.667</v>
+        <v>0</v>
       </c>
       <c r="D87" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>6.603</v>
+        <v>0.001</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="22" t="n">
         <v>0</v>
@@ -6174,38 +6304,44 @@
         <v>0</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="N87" s="22" t="n">
         <v>0</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>15.315</v>
+        <v>0.001</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>5.906</v>
+        <v>0.001</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>6.603</v>
+        <v>0.001</v>
       </c>
       <c r="W87" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>자판기 설치료 수입</t>
-        </is>
+          <t>배당금수익</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="22" t="n">
         <v>0</v>
@@ -6214,7 +6350,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="J88" s="22" t="n">
         <v>0</v>
@@ -6223,145 +6362,82 @@
         <v>0</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C89" s="22" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="D89" s="22" t="n">
-        <v>0.267</v>
+          <t>보험금 수익</t>
+        </is>
       </c>
       <c r="E89" s="22" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="F89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="22" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M89" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N89" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>0.431</v>
+        <v>0</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>-0.65</v>
+        <v>0.024</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X89" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="n">
-        <v>4.409</v>
-      </c>
-      <c r="D90" s="22" t="n">
-        <v>2.387</v>
-      </c>
-      <c r="E90" s="22" t="n">
-        <v>7.567</v>
-      </c>
-      <c r="F90" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G90" s="22" t="n">
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="22" t="n">
         <v>1</v>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M90" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" s="22" t="n">
-        <v>15.683</v>
-      </c>
-      <c r="U90" s="22" t="n">
-        <v>23.474</v>
-      </c>
-      <c r="V90" s="22" t="n">
-        <v>7.567</v>
-      </c>
-      <c r="W90" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X90" s="22" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>0.1</v>
+        <v>3.667</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>0.094</v>
+        <v>6.603</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="22" t="n">
         <v>0</v>
@@ -6373,2672 +6449,2765 @@
         <v>0</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T91" s="22" t="n">
-        <v>0</v>
+        <v>15.315</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>0.14</v>
+        <v>5.906</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>0.094</v>
+        <v>6.603</v>
       </c>
       <c r="W91" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>전자기록채권 매각손실</t>
-        </is>
+          <t>자판기 설치료 수입</t>
+        </is>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H92" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="22" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>지분법손실</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>13.896</v>
+        <v>0.742</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>12.321</v>
+        <v>0.267</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>4.761</v>
+        <v>-0.65</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="J93" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N93" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K93" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L93" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="M93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="22" t="n">
-        <v>0</v>
+      <c r="T93" s="22" t="n">
+        <v>0.368</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>4.761</v>
+        <v>-0.65</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>리스해약 손실</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>4.409</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>2.387</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0</v>
+        <v>7.567</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>3</v>
       </c>
       <c r="T94" s="22" t="n">
-        <v>0</v>
+        <v>15.683</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>6.736</v>
+        <v>23.474</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>0</v>
+        <v>7.567</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X94" s="22" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>16.861</v>
+        <v>0</v>
       </c>
       <c r="U95" s="22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
-        </is>
-      </c>
-      <c r="T96" s="22" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="U96" s="22" t="n">
+          <t>전자기록채권 매각손실</t>
+        </is>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>세액공제 외 원천소득세</t>
-        </is>
-      </c>
-      <c r="T97" s="22" t="n">
+          <t>지분법손실</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>13.896</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>12.321</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>4.761</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>4.761</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="X97" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D98" s="22" t="n">
-        <v>0.08699999999999999</v>
+          <t>리스해약 손실</t>
+        </is>
       </c>
       <c r="E98" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="T98" s="22" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="U98" s="22" t="n">
-        <v>0.065</v>
+        <v>6.736</v>
       </c>
       <c r="V98" s="22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>14.056</v>
-      </c>
-      <c r="D99" s="22" t="n">
-        <v>12.483</v>
-      </c>
-      <c r="E99" s="22" t="n">
-        <v>4.955</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>56</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="22" t="n">
-        <v>11</v>
+          <t>상장 관련 비용</t>
+        </is>
       </c>
       <c r="T99" s="22" t="n">
-        <v>18.636</v>
+        <v>16.861</v>
       </c>
       <c r="U99" s="22" t="n">
-        <v>6.941</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>4.955</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>56</v>
-      </c>
-      <c r="X99" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>748.148</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>615.857</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>515.98</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>467</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>-64</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>441</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>204</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>471</v>
-      </c>
-      <c r="T100" s="12" t="n">
-        <v>479.651</v>
-      </c>
-      <c r="U100" s="12" t="n">
-        <v>737.694</v>
-      </c>
-      <c r="V100" s="12" t="n">
-        <v>515.98</v>
-      </c>
-      <c r="W100" s="12" t="n">
-        <v>-64</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>204</v>
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>주식교부비</t>
+        </is>
+      </c>
+      <c r="T100" s="22" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="U100" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
-        </is>
-      </c>
-      <c r="I101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" s="22" t="n">
+          <t>세액공제 외 원천소득세</t>
+        </is>
+      </c>
+      <c r="T101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="E102" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="J102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="M102" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="22" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="U102" s="22" t="n">
+        <v>0.065</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W102" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>지분변동이익</t>
-        </is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>14.056</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>0</v>
+        <v>12.483</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>0</v>
+        <v>4.955</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G103" s="22" t="n">
+        <v>7</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="M103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T103" s="22" t="n">
+        <v>18.636</v>
       </c>
       <c r="U103" s="22" t="n">
-        <v>0</v>
+        <v>6.941</v>
       </c>
       <c r="V103" s="22" t="n">
-        <v>0</v>
+        <v>4.955</v>
       </c>
       <c r="W103" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="X103" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>특별이익 합계</t>
-        </is>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>0</v>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>748.148</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>615.857</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>515.98</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>381</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>467</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>-64</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>441</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>204</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>471</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>479.651</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>737.694</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>515.98</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>-64</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>204</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="H105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="22" t="n">
-        <v>232</v>
-      </c>
-      <c r="L105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>232</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>0</v>
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G105" s="17">
+        <f>IF(OR(G104="",C104=""),"",IF(C104&lt;=0,"",IFERROR(G104/C104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H105" s="17">
+        <f>IF(OR(H104="",D104=""),"",IF(D104&lt;=0,"",IFERROR(H104/D104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I105" s="17">
+        <f>IF(OR(I104="",E104=""),"",IF(E104&lt;=0,"",IFERROR(I104/E104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J105" s="17">
+        <f>IF(OR(J104="",F104=""),"",IF(F104&lt;=0,"",IFERROR(J104/F104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF(OR(K104="",G104=""),"",IF(G104&lt;=0,"",IFERROR(K104/G104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L105" s="17">
+        <f>IF(OR(L104="",H104=""),"",IF(H104&lt;=0,"",IFERROR(L104/H104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M105" s="17">
+        <f>IF(OR(M104="",I104=""),"",IF(I104&lt;=0,"",IFERROR(M104/I104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N105" s="17">
+        <f>IF(OR(N104="",J104=""),"",IF(J104&lt;=0,"",IFERROR(N104/J104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T105" s="17">
+        <f>IF(OR(T104="",S104=""),"",IF(S104&lt;=0,"",IFERROR(T104/S104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U105" s="17">
+        <f>IF(OR(U104="",T104=""),"",IF(T104&lt;=0,"",IFERROR(U104/T104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V105" s="17">
+        <f>IF(OR(V104="",U104=""),"",IF(U104&lt;=0,"",IFERROR(V104/U104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W105" s="17">
+        <f>IF(OR(W104="",V104=""),"",IF(V104&lt;=0,"",IFERROR(W104/V104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X105" s="17">
+        <f>IF(OR(X104="",W104=""),"",IF(W104&lt;=0,"",IFERROR(X104/W104-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="D106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="22" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="F106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H106" s="22" t="n">
-        <v>0</v>
+          <t>고정자산 매각이익</t>
+        </is>
       </c>
       <c r="I106" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="J106" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T106" s="22" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="U106" s="22" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="V106" s="22" t="n">
-        <v>0.592</v>
+        <v>0</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C107" s="22" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="D107" s="22" t="n">
-        <v>0</v>
+          <t>투자유가증권 매각이익</t>
+        </is>
       </c>
       <c r="E107" s="22" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="F107" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H107" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="22" t="n">
-        <v>243</v>
-      </c>
-      <c r="J107" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K107" s="22" t="n">
-        <v>163</v>
-      </c>
-      <c r="L107" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M107" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N107" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" s="22" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="U107" s="22" t="n">
-        <v>0.168</v>
+        <v>0</v>
       </c>
       <c r="V107" s="22" t="n">
-        <v>0.592</v>
+        <v>0</v>
       </c>
       <c r="W107" s="22" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="X107" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="n">
-        <v>759.092</v>
-      </c>
-      <c r="D108" s="12" t="n">
-        <v>615.857</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>515.388</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>465</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>296</v>
-      </c>
-      <c r="I108" s="12" t="n">
-        <v>-308</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="K108" s="12" t="n">
-        <v>237</v>
-      </c>
-      <c r="L108" s="12" t="n">
-        <v>439</v>
-      </c>
-      <c r="M108" s="12" t="n">
-        <v>203</v>
-      </c>
-      <c r="N108" s="12" t="n">
-        <v>470</v>
-      </c>
-      <c r="T108" s="12" t="n">
-        <v>479.068</v>
-      </c>
-      <c r="U108" s="12" t="n">
-        <v>737.526</v>
-      </c>
-      <c r="V108" s="12" t="n">
-        <v>515.388</v>
-      </c>
-      <c r="W108" s="12" t="n">
-        <v>-308</v>
-      </c>
-      <c r="X108" s="12" t="n">
-        <v>203</v>
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>지분변동이익</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>341.903</v>
+          <t>특별이익 합계</t>
+        </is>
       </c>
       <c r="D109" s="22" t="n">
-        <v>113.593</v>
+        <v>0</v>
       </c>
       <c r="E109" s="22" t="n">
-        <v>124.363</v>
-      </c>
-      <c r="F109" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H109" s="22" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>149</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <v>187</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M109" s="22" t="n">
-        <v>253</v>
-      </c>
-      <c r="N109" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>186.775</v>
+        <v>0</v>
       </c>
       <c r="U109" s="22" t="n">
-        <v>167.001</v>
+        <v>0</v>
       </c>
       <c r="V109" s="22" t="n">
-        <v>124.363</v>
+        <v>0</v>
       </c>
       <c r="W109" s="22" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="X109" s="22" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C110" s="22" t="n">
-        <v>-100.03</v>
-      </c>
-      <c r="D110" s="22" t="n">
-        <v>83.794</v>
-      </c>
-      <c r="E110" s="22" t="n">
-        <v>-65.544</v>
-      </c>
-      <c r="F110" s="22" t="n">
-        <v>97</v>
-      </c>
-      <c r="G110" s="22" t="n">
-        <v>-77</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="H110" s="22" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I110" s="22" t="n">
-        <v>-164</v>
-      </c>
-      <c r="J110" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="K110" s="22" t="n">
-        <v>-97</v>
+        <v>232</v>
       </c>
       <c r="L110" s="22" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>-95</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="T110" s="22" t="n">
-        <v>-45.466</v>
-      </c>
-      <c r="U110" s="22" t="n">
-        <v>-81.827</v>
-      </c>
-      <c r="V110" s="22" t="n">
-        <v>-65.544</v>
+        <v>0</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>-164</v>
+        <v>232</v>
       </c>
       <c r="X110" s="22" t="n">
-        <v>-95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="C111" s="22" t="n">
-        <v>241.873</v>
+        <v>2.727</v>
       </c>
       <c r="D111" s="22" t="n">
-        <v>197.387</v>
+        <v>0</v>
       </c>
       <c r="E111" s="22" t="n">
-        <v>58.819</v>
+        <v>0.592</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="G111" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" s="22" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="U111" s="22" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>243</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" s="22" t="n">
         <v>163</v>
       </c>
-      <c r="H111" s="22" t="n">
-        <v>102</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>45</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>90</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>146</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>157</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>162</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>141.309</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>85.17400000000001</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>58.819</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>-16</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="n">
-        <v>517.2190000000001</v>
-      </c>
-      <c r="D112" s="12" t="n">
-        <v>418.47</v>
-      </c>
-      <c r="E112" s="12" t="n">
-        <v>456.569</v>
-      </c>
-      <c r="F112" s="12" t="n">
-        <v>257</v>
-      </c>
-      <c r="G112" s="12" t="n">
-        <v>303</v>
-      </c>
-      <c r="H112" s="12" t="n">
-        <v>193</v>
-      </c>
-      <c r="I112" s="12" t="n">
-        <v>-292</v>
-      </c>
-      <c r="J112" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="K112" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="L112" s="12" t="n">
-        <v>293</v>
-      </c>
-      <c r="M112" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="N112" s="12" t="n">
-        <v>307</v>
-      </c>
-      <c r="T112" s="12" t="n">
-        <v>337.759</v>
-      </c>
-      <c r="U112" s="12" t="n">
-        <v>652.352</v>
-      </c>
-      <c r="V112" s="12" t="n">
-        <v>456.569</v>
-      </c>
-      <c r="W112" s="12" t="n">
-        <v>-292</v>
-      </c>
-      <c r="X112" s="12" t="n">
-        <v>46</v>
+      <c r="L112" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" s="22" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="W112" s="22" t="n">
+        <v>243</v>
+      </c>
+      <c r="X112" s="22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>759.092</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>615.857</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>515.388</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>381</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>465</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>296</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>-308</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>237</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>439</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>203</v>
+      </c>
+      <c r="N113" s="12" t="n">
+        <v>470</v>
+      </c>
+      <c r="T113" s="12" t="n">
+        <v>479.068</v>
+      </c>
+      <c r="U113" s="12" t="n">
+        <v>737.526</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>515.388</v>
+      </c>
+      <c r="W113" s="12" t="n">
+        <v>-308</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C114" s="22" t="n">
+        <v>341.903</v>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>113.593</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>124.363</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="G114" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="I114" s="22" t="n">
+        <v>149</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>187</v>
+      </c>
+      <c r="L114" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="M114" s="22" t="n">
+        <v>253</v>
+      </c>
+      <c r="N114" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="T114" s="22" t="n">
+        <v>186.775</v>
+      </c>
+      <c r="U114" s="22" t="n">
+        <v>167.001</v>
+      </c>
+      <c r="V114" s="22" t="n">
+        <v>124.363</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>149</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n">
+        <v>-100.03</v>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>83.794</v>
+      </c>
+      <c r="E115" s="22" t="n">
+        <v>-65.544</v>
+      </c>
+      <c r="F115" s="22" t="n">
+        <v>97</v>
+      </c>
+      <c r="G115" s="22" t="n">
+        <v>-77</v>
+      </c>
+      <c r="H115" s="22" t="n">
+        <v>84</v>
+      </c>
+      <c r="I115" s="22" t="n">
+        <v>-164</v>
+      </c>
+      <c r="J115" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="K115" s="22" t="n">
+        <v>-97</v>
+      </c>
+      <c r="L115" s="22" t="n">
+        <v>86</v>
+      </c>
+      <c r="M115" s="22" t="n">
+        <v>-95</v>
+      </c>
+      <c r="N115" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T115" s="22" t="n">
+        <v>-45.466</v>
+      </c>
+      <c r="U115" s="22" t="n">
+        <v>-81.827</v>
+      </c>
+      <c r="V115" s="22" t="n">
+        <v>-65.544</v>
+      </c>
+      <c r="W115" s="22" t="n">
+        <v>-164</v>
+      </c>
+      <c r="X115" s="22" t="n">
+        <v>-95</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C116" s="22" t="n">
+        <v>241.873</v>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>197.387</v>
+      </c>
+      <c r="E116" s="22" t="n">
+        <v>58.819</v>
+      </c>
+      <c r="F116" s="22" t="n">
+        <v>123</v>
+      </c>
+      <c r="G116" s="22" t="n">
+        <v>163</v>
+      </c>
+      <c r="H116" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J116" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="K116" s="22" t="n">
+        <v>90</v>
+      </c>
+      <c r="L116" s="22" t="n">
+        <v>146</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>157</v>
+      </c>
+      <c r="N116" s="22" t="n">
+        <v>162</v>
+      </c>
+      <c r="T116" s="22" t="n">
+        <v>141.309</v>
+      </c>
+      <c r="U116" s="22" t="n">
+        <v>85.17400000000001</v>
+      </c>
+      <c r="V116" s="22" t="n">
+        <v>58.819</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>517.2190000000001</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>418.47</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>456.569</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>257</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>303</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>-292</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>293</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="N117" s="12" t="n">
+        <v>307</v>
+      </c>
+      <c r="T117" s="12" t="n">
+        <v>337.759</v>
+      </c>
+      <c r="U117" s="12" t="n">
+        <v>652.352</v>
+      </c>
+      <c r="V117" s="12" t="n">
+        <v>456.569</v>
+      </c>
+      <c r="W117" s="12" t="n">
+        <v>-292</v>
+      </c>
+      <c r="X117" s="12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G118" s="17">
+        <f>IF(OR(G117="",C117=""),"",IF(C117&lt;=0,"",IFERROR(G117/C117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H118" s="17">
+        <f>IF(OR(H117="",D117=""),"",IF(D117&lt;=0,"",IFERROR(H117/D117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I118" s="17">
+        <f>IF(OR(I117="",E117=""),"",IF(E117&lt;=0,"",IFERROR(I117/E117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J118" s="17">
+        <f>IF(OR(J117="",F117=""),"",IF(F117&lt;=0,"",IFERROR(J117/F117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF(OR(K117="",G117=""),"",IF(G117&lt;=0,"",IFERROR(K117/G117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L118" s="17">
+        <f>IF(OR(L117="",H117=""),"",IF(H117&lt;=0,"",IFERROR(L117/H117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M118" s="17">
+        <f>IF(OR(M117="",I117=""),"",IF(I117&lt;=0,"",IFERROR(M117/I117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N118" s="17">
+        <f>IF(OR(N117="",J117=""),"",IF(J117&lt;=0,"",IFERROR(N117/J117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T118" s="17">
+        <f>IF(OR(T117="",S117=""),"",IF(S117&lt;=0,"",IFERROR(T117/S117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U118" s="17">
+        <f>IF(OR(U117="",T117=""),"",IF(T117&lt;=0,"",IFERROR(U117/T117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V118" s="17">
+        <f>IF(OR(V117="",U117=""),"",IF(U117&lt;=0,"",IFERROR(V117/U117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W118" s="17">
+        <f>IF(OR(W117="",V117=""),"",IF(V117&lt;=0,"",IFERROR(W117/V117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X118" s="17">
+        <f>IF(OR(X117="",W117=""),"",IF(W117&lt;=0,"",IFERROR(X117/W117-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 순손익</t>
         </is>
       </c>
-      <c r="E113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="12" t="n">
+      <c r="E119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I113" s="12" t="n">
+      <c r="I119" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="J119" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="K113" s="12" t="n">
+      <c r="K119" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="L113" s="12" t="n">
+      <c r="L119" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M113" s="12" t="n">
+      <c r="M119" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N113" s="12" t="n">
+      <c r="N119" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="V113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="12" t="n">
+      <c r="V119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="X113" s="12" t="n">
+      <c r="X119" s="12" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="C114" s="12" t="n">
+      <c r="C120" s="12" t="n">
         <v>517.2190000000001</v>
       </c>
-      <c r="D114" s="12" t="n">
+      <c r="D120" s="12" t="n">
         <v>418.47</v>
       </c>
-      <c r="E114" s="12" t="n">
+      <c r="E120" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="F114" s="12" t="n">
+      <c r="F120" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="G114" s="12" t="n">
+      <c r="G120" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H120" s="12" t="n">
         <v>188</v>
       </c>
-      <c r="I114" s="12" t="n">
+      <c r="I120" s="12" t="n">
         <v>-296</v>
       </c>
-      <c r="J114" s="12" t="n">
+      <c r="J120" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K114" s="12" t="n">
+      <c r="K120" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="L114" s="12" t="n">
+      <c r="L120" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="M114" s="12" t="n">
+      <c r="M120" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="N114" s="12" t="n">
+      <c r="N120" s="12" t="n">
         <v>299</v>
       </c>
-      <c r="T114" s="12" t="n">
+      <c r="T120" s="12" t="n">
         <v>337.759</v>
       </c>
-      <c r="U114" s="12" t="n">
+      <c r="U120" s="12" t="n">
         <v>652.352</v>
       </c>
-      <c r="V114" s="12" t="n">
+      <c r="V120" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="W114" s="12" t="n">
+      <c r="W120" s="12" t="n">
         <v>-296</v>
       </c>
-      <c r="X114" s="12" t="n">
+      <c r="X120" s="12" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G121" s="17">
+        <f>IF(OR(G120="",C120=""),"",IF(C120&lt;=0,"",IFERROR(G120/C120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H121" s="17">
+        <f>IF(OR(H120="",D120=""),"",IF(D120&lt;=0,"",IFERROR(H120/D120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I121" s="17">
+        <f>IF(OR(I120="",E120=""),"",IF(E120&lt;=0,"",IFERROR(I120/E120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J121" s="17">
+        <f>IF(OR(J120="",F120=""),"",IF(F120&lt;=0,"",IFERROR(J120/F120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K121" s="17">
+        <f>IF(OR(K120="",G120=""),"",IF(G120&lt;=0,"",IFERROR(K120/G120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L121" s="17">
+        <f>IF(OR(L120="",H120=""),"",IF(H120&lt;=0,"",IFERROR(L120/H120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M121" s="17">
+        <f>IF(OR(M120="",I120=""),"",IF(I120&lt;=0,"",IFERROR(M120/I120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N121" s="17">
+        <f>IF(OR(N120="",J120=""),"",IF(J120&lt;=0,"",IFERROR(N120/J120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T121" s="17">
+        <f>IF(OR(T120="",S120=""),"",IF(S120&lt;=0,"",IFERROR(T120/S120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U121" s="17">
+        <f>IF(OR(U120="",T120=""),"",IF(T120&lt;=0,"",IFERROR(U120/T120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V121" s="17">
+        <f>IF(OR(V120="",U120=""),"",IF(U120&lt;=0,"",IFERROR(V120/U120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W121" s="17">
+        <f>IF(OR(W120="",V120=""),"",IF(V120&lt;=0,"",IFERROR(W120/V120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X121" s="17">
+        <f>IF(OR(X120="",W120=""),"",IF(W120&lt;=0,"",IFERROR(X120/W120-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B116" s="44" t="inlineStr">
+      <c r="B123" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-      <c r="J116" s="18" t="n"/>
-      <c r="K116" s="18" t="n"/>
-      <c r="L116" s="18" t="n"/>
-      <c r="M116" s="18" t="n"/>
-      <c r="N116" s="18" t="n"/>
-      <c r="O116" s="18" t="n"/>
-      <c r="P116" s="18" t="n"/>
-      <c r="Q116" s="18" t="n"/>
-      <c r="R116" s="18" t="n"/>
-      <c r="S116" s="18" t="n"/>
-      <c r="T116" s="18" t="n"/>
-      <c r="U116" s="18" t="n"/>
-      <c r="V116" s="18" t="n"/>
-      <c r="W116" s="18" t="n"/>
-      <c r="X116" s="18" t="n"/>
-      <c r="Y116" s="18" t="n"/>
-      <c r="Z116" s="18" t="n"/>
-      <c r="AA116" s="18" t="n"/>
-      <c r="AB116" s="18" t="n"/>
-      <c r="AC116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+      <c r="J123" s="18" t="n"/>
+      <c r="K123" s="18" t="n"/>
+      <c r="L123" s="18" t="n"/>
+      <c r="M123" s="18" t="n"/>
+      <c r="N123" s="18" t="n"/>
+      <c r="O123" s="18" t="n"/>
+      <c r="P123" s="18" t="n"/>
+      <c r="Q123" s="18" t="n"/>
+      <c r="R123" s="18" t="n"/>
+      <c r="S123" s="18" t="n"/>
+      <c r="T123" s="18" t="n"/>
+      <c r="U123" s="18" t="n"/>
+      <c r="V123" s="18" t="n"/>
+      <c r="W123" s="18" t="n"/>
+      <c r="X123" s="18" t="n"/>
+      <c r="Y123" s="18" t="n"/>
+      <c r="Z123" s="18" t="n"/>
+      <c r="AA123" s="18" t="n"/>
+      <c r="AB123" s="18" t="n"/>
+      <c r="AC123" s="18" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I124" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
+      <c r="J124" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K117" s="5" t="inlineStr">
+      <c r="K124" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L117" s="5" t="inlineStr">
+      <c r="L124" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M117" s="5" t="inlineStr">
+      <c r="M124" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N117" s="5" t="inlineStr">
+      <c r="N124" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O117" s="5" t="inlineStr">
+      <c r="O124" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P117" s="5" t="inlineStr">
+      <c r="P124" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q117" s="5" t="inlineStr">
+      <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R117" s="5" t="inlineStr">
+      <c r="R124" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S117" s="5" t="inlineStr">
+      <c r="S124" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T117" s="5" t="inlineStr">
+      <c r="T124" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U117" s="5" t="inlineStr">
+      <c r="U124" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V117" s="5" t="inlineStr">
+      <c r="V124" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W117" s="5" t="inlineStr">
+      <c r="W124" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X117" s="5" t="inlineStr">
+      <c r="X124" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y117" s="5" t="inlineStr">
+      <c r="Y124" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z117" s="5" t="inlineStr">
+      <c r="Z124" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA117" s="5" t="inlineStr">
+      <c r="AA124" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB117" s="5" t="inlineStr">
+      <c r="AB124" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC117" s="5" t="inlineStr">
+      <c r="AC124" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C118" s="12" t="n">
+      <c r="C125" s="12" t="n">
         <v>517.2190000000001</v>
       </c>
-      <c r="D118" s="12" t="n">
+      <c r="D125" s="12" t="n">
         <v>418.47</v>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="E125" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="F118" s="12" t="n">
+      <c r="F125" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="G118" s="12" t="n">
+      <c r="G125" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H125" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="I118" s="12" t="n">
+      <c r="I125" s="12" t="n">
         <v>-292</v>
       </c>
-      <c r="J118" s="12" t="n">
+      <c r="J125" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="K118" s="12" t="n">
+      <c r="K125" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="L118" s="12" t="n">
+      <c r="L125" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="M118" s="12" t="n">
+      <c r="M125" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="N118" s="12" t="n">
+      <c r="N125" s="12" t="n">
         <v>307</v>
       </c>
-      <c r="T118" s="12" t="n">
+      <c r="T125" s="12" t="n">
         <v>337.759</v>
       </c>
-      <c r="U118" s="12" t="n">
+      <c r="U125" s="12" t="n">
         <v>652.352</v>
       </c>
-      <c r="V118" s="12" t="n">
+      <c r="V125" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="W118" s="12" t="n">
+      <c r="W125" s="12" t="n">
         <v>-292</v>
       </c>
-      <c r="X118" s="12" t="n">
+      <c r="X125" s="12" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>해외사업환산조정</t>
         </is>
       </c>
-      <c r="J119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" s="22" t="n">
+      <c r="J126" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="22" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="20" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="J120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" s="22" t="n">
+      <c r="J127" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="22" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C121" s="12" t="n">
+      <c r="C128" s="12" t="n">
         <v>517.2190000000001</v>
       </c>
-      <c r="D121" s="12" t="n">
+      <c r="D128" s="12" t="n">
         <v>418.47</v>
       </c>
-      <c r="E121" s="12" t="n">
+      <c r="E128" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="F121" s="12" t="n">
+      <c r="F128" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="G121" s="12" t="n">
+      <c r="G128" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="H121" s="12" t="n">
+      <c r="H128" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="I121" s="12" t="n">
+      <c r="I128" s="12" t="n">
         <v>-292</v>
       </c>
-      <c r="J121" s="12" t="n">
+      <c r="J128" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="K121" s="12" t="n">
+      <c r="K128" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="L121" s="12" t="n">
+      <c r="L128" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="M121" s="12" t="n">
+      <c r="M128" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="N121" s="12" t="n">
+      <c r="N128" s="12" t="n">
         <v>327</v>
       </c>
-      <c r="T121" s="12" t="n">
+      <c r="T128" s="12" t="n">
         <v>337.759</v>
       </c>
-      <c r="U121" s="12" t="n">
+      <c r="U128" s="12" t="n">
         <v>652.352</v>
       </c>
-      <c r="V121" s="12" t="n">
+      <c r="V128" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="W121" s="12" t="n">
+      <c r="W128" s="12" t="n">
         <v>-292</v>
       </c>
-      <c r="X121" s="12" t="n">
+      <c r="X128" s="12" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C122" s="12" t="n">
+      <c r="C129" s="12" t="n">
         <v>517.2190000000001</v>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D129" s="12" t="n">
         <v>418.47</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="E129" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="F129" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="G129" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>188</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="I129" s="12" t="n">
         <v>-296</v>
       </c>
-      <c r="J122" s="12" t="n">
+      <c r="J129" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K122" s="12" t="n">
+      <c r="K129" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="L122" s="12" t="n">
+      <c r="L129" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="M122" s="12" t="n">
+      <c r="M129" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="N122" s="12" t="n">
+      <c r="N129" s="12" t="n">
         <v>317</v>
       </c>
-      <c r="T122" s="12" t="n">
+      <c r="T129" s="12" t="n">
         <v>337.759</v>
       </c>
-      <c r="U122" s="12" t="n">
+      <c r="U129" s="12" t="n">
         <v>652.352</v>
       </c>
-      <c r="V122" s="12" t="n">
+      <c r="V129" s="12" t="n">
         <v>456.569</v>
       </c>
-      <c r="W122" s="12" t="n">
+      <c r="W129" s="12" t="n">
         <v>-296</v>
       </c>
-      <c r="X122" s="12" t="n">
+      <c r="X129" s="12" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="E123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="12" t="n">
+      <c r="E130" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I123" s="12" t="n">
+      <c r="I130" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J123" s="12" t="n">
+      <c r="J130" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="K123" s="12" t="n">
+      <c r="K130" s="12" t="n">
         <v>-1</v>
       </c>
-      <c r="L123" s="12" t="n">
+      <c r="L130" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M123" s="12" t="n">
+      <c r="M130" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N123" s="12" t="n">
+      <c r="N130" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="V123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" s="12" t="n">
+      <c r="V130" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="X123" s="12" t="n">
+      <c r="X130" s="12" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="18" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B125" s="44" t="inlineStr">
+      <c r="B132" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C125" s="18" t="n"/>
-      <c r="D125" s="18" t="n"/>
-      <c r="E125" s="18" t="n"/>
-      <c r="F125" s="18" t="n"/>
-      <c r="G125" s="18" t="n"/>
-      <c r="H125" s="18" t="n"/>
-      <c r="I125" s="18" t="n"/>
-      <c r="J125" s="18" t="n"/>
-      <c r="K125" s="18" t="n"/>
-      <c r="L125" s="18" t="n"/>
-      <c r="M125" s="18" t="n"/>
-      <c r="N125" s="18" t="n"/>
-      <c r="O125" s="18" t="n"/>
-      <c r="P125" s="18" t="n"/>
-      <c r="Q125" s="18" t="n"/>
-      <c r="R125" s="18" t="n"/>
-      <c r="S125" s="18" t="n"/>
-      <c r="T125" s="18" t="n"/>
-      <c r="U125" s="18" t="n"/>
-      <c r="V125" s="18" t="n"/>
-      <c r="W125" s="18" t="n"/>
-      <c r="X125" s="18" t="n"/>
-      <c r="Y125" s="18" t="n"/>
-      <c r="Z125" s="18" t="n"/>
-      <c r="AA125" s="18" t="n"/>
-      <c r="AB125" s="18" t="n"/>
-      <c r="AC125" s="18" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="C132" s="18" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="18" t="n"/>
+      <c r="G132" s="18" t="n"/>
+      <c r="H132" s="18" t="n"/>
+      <c r="I132" s="18" t="n"/>
+      <c r="J132" s="18" t="n"/>
+      <c r="K132" s="18" t="n"/>
+      <c r="L132" s="18" t="n"/>
+      <c r="M132" s="18" t="n"/>
+      <c r="N132" s="18" t="n"/>
+      <c r="O132" s="18" t="n"/>
+      <c r="P132" s="18" t="n"/>
+      <c r="Q132" s="18" t="n"/>
+      <c r="R132" s="18" t="n"/>
+      <c r="S132" s="18" t="n"/>
+      <c r="T132" s="18" t="n"/>
+      <c r="U132" s="18" t="n"/>
+      <c r="V132" s="18" t="n"/>
+      <c r="W132" s="18" t="n"/>
+      <c r="X132" s="18" t="n"/>
+      <c r="Y132" s="18" t="n"/>
+      <c r="Z132" s="18" t="n"/>
+      <c r="AA132" s="18" t="n"/>
+      <c r="AB132" s="18" t="n"/>
+      <c r="AC132" s="18" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J126" s="5" t="inlineStr">
+      <c r="J133" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K126" s="5" t="inlineStr">
+      <c r="K133" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="L133" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M126" s="5" t="inlineStr">
+      <c r="M133" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="N133" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O126" s="5" t="inlineStr">
+      <c r="O133" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P126" s="5" t="inlineStr">
+      <c r="P133" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q126" s="5" t="inlineStr">
+      <c r="Q133" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R126" s="5" t="inlineStr">
+      <c r="R133" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S126" s="5" t="inlineStr">
+      <c r="S133" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T126" s="5" t="inlineStr">
+      <c r="T133" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U126" s="5" t="inlineStr">
+      <c r="U133" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V126" s="5" t="inlineStr">
+      <c r="V133" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W126" s="5" t="inlineStr">
+      <c r="W133" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X126" s="5" t="inlineStr">
+      <c r="X133" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y126" s="5" t="inlineStr">
+      <c r="Y133" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z126" s="5" t="inlineStr">
+      <c r="Z133" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA126" s="5" t="inlineStr">
+      <c r="AA133" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB126" s="5" t="inlineStr">
+      <c r="AB133" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC126" s="5" t="inlineStr">
+      <c r="AC133" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C127" s="12" t="n">
+      <c r="C134" s="12" t="n">
         <v>1406.188</v>
       </c>
-      <c r="E127" s="12" t="n">
+      <c r="E134" s="12" t="n">
         <v>2537.433</v>
       </c>
-      <c r="G127" s="12" t="n">
+      <c r="G134" s="12" t="n">
         <v>846</v>
       </c>
-      <c r="I127" s="12" t="n">
+      <c r="I134" s="12" t="n">
         <v>834</v>
       </c>
-      <c r="K127" s="12" t="n">
+      <c r="K134" s="12" t="n">
         <v>371</v>
       </c>
-      <c r="M127" s="12" t="n">
+      <c r="M134" s="12" t="n">
         <v>1013</v>
       </c>
-      <c r="S127" s="12" t="n">
+      <c r="S134" s="12" t="n">
         <v>2164.291</v>
       </c>
-      <c r="T127" s="12" t="n">
+      <c r="T134" s="12" t="n">
         <v>2590.056</v>
       </c>
-      <c r="U127" s="12" t="n">
+      <c r="U134" s="12" t="n">
         <v>2268.893</v>
       </c>
-      <c r="V127" s="12" t="n">
+      <c r="V134" s="12" t="n">
         <v>2537.433</v>
       </c>
-      <c r="W127" s="12" t="n">
+      <c r="W134" s="12" t="n">
         <v>834</v>
       </c>
-      <c r="X127" s="12" t="n">
+      <c r="X134" s="12" t="n">
         <v>1013</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C128" s="22" t="n">
-        <v>136.272</v>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>296.356</v>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>164</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>390</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>276</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>492</v>
-      </c>
-      <c r="S128" s="22" t="n">
-        <v>172.895</v>
-      </c>
-      <c r="T128" s="22" t="n">
-        <v>195.208</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>223.665</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>296.356</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>390</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>7.671</v>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="G129" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>12.718</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>5.648</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>8.169</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="E130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K130" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="n">
-        <v>51.142</v>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>23.846</v>
-      </c>
-      <c r="G131" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K131" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="S131" s="22" t="n">
-        <v>-22.282</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>34.708</v>
-      </c>
-      <c r="U131" s="22" t="n">
-        <v>-48.613</v>
-      </c>
-      <c r="V131" s="22" t="n">
-        <v>23.846</v>
-      </c>
-      <c r="W131" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="20" t="inlineStr">
-        <is>
-          <t>임원 주식급여 충당금 증감</t>
-        </is>
-      </c>
-      <c r="S132" s="22" t="n">
-        <v>-4.079</v>
-      </c>
-      <c r="T132" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="20" t="inlineStr">
-        <is>
-          <t>주주우대 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" s="22" t="n">
-        <v>74.625</v>
-      </c>
-      <c r="G133" s="22" t="n">
-        <v>-74</v>
-      </c>
-      <c r="I133" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="K133" s="22" t="n">
-        <v>-197</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>74.625</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="C134" s="22" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="E134" s="22" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="G134" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I134" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K134" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="S134" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T134" s="22" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="U134" s="22" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="V134" s="22" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="W134" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>-0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>보험금 수익</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
+        <v>136.272</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>-2.144</v>
+        <v>296.356</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>164</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>0</v>
+        <v>390</v>
+      </c>
+      <c r="K135" s="22" t="n">
+        <v>276</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>-6</v>
+        <v>492</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>0</v>
+        <v>172.895</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>-5.649</v>
+        <v>195.208</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>0</v>
+        <v>223.665</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>-2.144</v>
+        <v>296.356</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>-6</v>
+        <v>492</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
-        </is>
+          <t>영업권 상각</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>7.671</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>0</v>
+        <v>12.06</v>
+      </c>
+      <c r="G136" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>-1</v>
+        <v>8</v>
+      </c>
+      <c r="K136" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="S136" s="22" t="n">
+        <v>12.718</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>5.648</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>8.169</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>0</v>
+        <v>12.06</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C137" s="22" t="n">
-        <v>-4.564</v>
+          <t>대손충당금 증감</t>
+        </is>
       </c>
       <c r="E137" s="22" t="n">
-        <v>-11.167</v>
+        <v>0</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>-13</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>-37.041</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>-53.906</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>-42.684</v>
+        <v>-0</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>-11.167</v>
+        <v>0</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>-13</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>보전금 수익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C138" s="22" t="n">
+        <v>51.142</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>0</v>
+        <v>23.846</v>
+      </c>
+      <c r="G138" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I138" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K138" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="S138" s="22" t="n">
+        <v>-22.282</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>0</v>
+        <v>34.708</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>-17.136</v>
+        <v>-48.613</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>0</v>
+        <v>23.846</v>
+      </c>
+      <c r="W138" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="X138" s="22" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>리스해약 손실</t>
-        </is>
-      </c>
-      <c r="E139" s="22" t="n">
-        <v>0</v>
+          <t>임원 주식급여 충당금 증감</t>
+        </is>
+      </c>
+      <c r="S139" s="22" t="n">
+        <v>-4.079</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" s="22" t="n">
-        <v>17.136</v>
-      </c>
-      <c r="V139" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>주주우대 충당금 증감</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>0.197</v>
+        <v>0</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>0.366</v>
+        <v>74.625</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>0</v>
+        <v>-74</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>0</v>
+        <v>-197</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="22" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="T140" s="22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>0.366</v>
+        <v>74.625</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="C141" s="22" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="G141" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K141" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M141" s="22" t="n">
+        <v>-0</v>
       </c>
       <c r="S141" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T141" s="22" t="n">
-        <v>20.861</v>
+        <v>-0.001</v>
+      </c>
+      <c r="U141" s="22" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
+          <t>보험금 수익</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="n">
+        <v>-2.144</v>
+      </c>
+      <c r="I142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="S142" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>20.861</v>
+        <v>-5.649</v>
       </c>
       <c r="U142" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="V142" s="22" t="n">
+        <v>-2.144</v>
+      </c>
+      <c r="W142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" s="22" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
-        </is>
-      </c>
-      <c r="S143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" s="22" t="n">
-        <v>13.246</v>
-      </c>
-      <c r="U143" s="22" t="n">
+          <t>보상금 수취</t>
+        </is>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X143" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>지분법손익</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>13.896</v>
+        <v>-4.564</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>30.978</v>
+        <v>-11.167</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>73</v>
+        <v>-5</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>12</v>
+        <v>-13</v>
+      </c>
+      <c r="S144" s="22" t="n">
+        <v>-37.041</v>
+      </c>
+      <c r="T144" s="22" t="n">
+        <v>-53.906</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>0</v>
+        <v>-42.684</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>30.978</v>
+        <v>-11.167</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>73</v>
+        <v>-5</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>12</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
+          <t>보전금 수익</t>
         </is>
       </c>
       <c r="E145" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I145" s="22" t="n">
-        <v>-75</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>0</v>
+      <c r="T145" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" s="22" t="n">
+        <v>-17.136</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>-75</v>
-      </c>
-      <c r="X145" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>지분변동손익</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="n">
-        <v>-13.671</v>
+          <t>리스해약 손실</t>
+        </is>
       </c>
       <c r="E146" s="22" t="n">
-        <v>-13.671</v>
-      </c>
-      <c r="G146" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>0</v>
+        <v>17.136</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>-13.671</v>
-      </c>
-      <c r="W146" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n">
+        <v>0.197</v>
       </c>
       <c r="E147" s="22" t="n">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="G147" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M147" s="22" t="n">
-        <v>161</v>
+        <v>0</v>
+      </c>
+      <c r="S147" s="22" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>0.24</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손익</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E148" s="22" t="n">
-        <v>3.662</v>
-      </c>
-      <c r="G148" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I148" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="K148" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M148" s="22" t="n">
-        <v>5</v>
+          <t>상장 관련 비용</t>
+        </is>
       </c>
       <c r="S148" s="22" t="n">
-        <v>2.992</v>
+        <v>0</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>1.431</v>
-      </c>
-      <c r="U148" s="22" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="V148" s="22" t="n">
-        <v>3.662</v>
-      </c>
-      <c r="W148" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="X148" s="22" t="n">
-        <v>5</v>
+        <v>20.861</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="C149" s="22" t="n">
-        <v>-372.761</v>
-      </c>
-      <c r="E149" s="22" t="n">
-        <v>-93.402</v>
-      </c>
-      <c r="G149" s="22" t="n">
-        <v>-174</v>
-      </c>
-      <c r="I149" s="22" t="n">
-        <v>84</v>
-      </c>
-      <c r="K149" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="M149" s="22" t="n">
-        <v>-240</v>
-      </c>
-      <c r="S149" s="22" t="n">
-        <v>-251.056</v>
+          <t>상장 관련 비용</t>
+        </is>
       </c>
       <c r="T149" s="22" t="n">
-        <v>-43.738</v>
+        <v>20.861</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>-629.905</v>
-      </c>
-      <c r="V149" s="22" t="n">
-        <v>-93.402</v>
-      </c>
-      <c r="W149" s="22" t="n">
-        <v>84</v>
-      </c>
-      <c r="X149" s="22" t="n">
-        <v>-240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="C150" s="22" t="n">
-        <v>26.155</v>
-      </c>
-      <c r="E150" s="22" t="n">
-        <v>26.411</v>
-      </c>
-      <c r="G150" s="22" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I150" s="22" t="n">
-        <v>-59</v>
-      </c>
-      <c r="K150" s="22" t="n">
-        <v>-36</v>
-      </c>
-      <c r="M150" s="22" t="n">
-        <v>59</v>
+          <t>주식교부비</t>
+        </is>
       </c>
       <c r="S150" s="22" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="T150" s="22" t="n">
-        <v>-1.503</v>
+        <v>13.246</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>-27.628</v>
-      </c>
-      <c r="V150" s="22" t="n">
-        <v>26.411</v>
-      </c>
-      <c r="W150" s="22" t="n">
-        <v>-59</v>
-      </c>
-      <c r="X150" s="22" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여부채 증감</t>
+          <t>지분법손익</t>
         </is>
       </c>
       <c r="C151" s="22" t="n">
-        <v>0.287</v>
+        <v>13.896</v>
       </c>
       <c r="E151" s="22" t="n">
-        <v>0.623</v>
+        <v>30.978</v>
       </c>
       <c r="G151" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K151" s="22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>-0.307</v>
+        <v>0</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>0.623</v>
+        <v>30.978</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
-        </is>
-      </c>
-      <c r="C152" s="22" t="n">
-        <v>19.879</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
       </c>
       <c r="E152" s="22" t="n">
-        <v>-15.344</v>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K152" s="22" t="n">
-        <v>-9</v>
+        <v>-75</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="S152" s="22" t="n">
-        <v>-67.82599999999999</v>
-      </c>
-      <c r="T152" s="22" t="n">
-        <v>-31.882</v>
-      </c>
-      <c r="U152" s="22" t="n">
-        <v>-57.415</v>
+        <v>0</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>-15.344</v>
+        <v>0</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>-12</v>
+        <v>-75</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>영업채무 증감</t>
+          <t>지분변동손익</t>
         </is>
       </c>
       <c r="C153" s="22" t="n">
-        <v>36.037</v>
+        <v>-13.671</v>
       </c>
       <c r="E153" s="22" t="n">
-        <v>-22.342</v>
+        <v>-13.671</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-62</v>
-      </c>
-      <c r="K153" s="22" t="n">
-        <v>-32</v>
-      </c>
-      <c r="M153" s="22" t="n">
-        <v>66</v>
-      </c>
-      <c r="S153" s="22" t="n">
-        <v>331.266</v>
-      </c>
-      <c r="T153" s="22" t="n">
-        <v>-84.955</v>
+        <v>0</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>332.456</v>
+        <v>0</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>-22.342</v>
+        <v>-13.671</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-62</v>
-      </c>
-      <c r="X153" s="22" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="C154" s="22" t="n">
-        <v>83.214</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="E154" s="22" t="n">
-        <v>266.105</v>
+        <v>0</v>
       </c>
       <c r="G154" s="22" t="n">
-        <v>-118</v>
+        <v>0</v>
       </c>
       <c r="I154" s="22" t="n">
-        <v>-200</v>
+        <v>232</v>
       </c>
       <c r="K154" s="22" t="n">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="M154" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="S154" s="22" t="n">
-        <v>-0.331</v>
-      </c>
-      <c r="T154" s="22" t="n">
-        <v>-99.23999999999999</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>-50.501</v>
+        <v>161</v>
       </c>
       <c r="V154" s="22" t="n">
-        <v>266.105</v>
+        <v>0</v>
       </c>
       <c r="W154" s="22" t="n">
-        <v>-200</v>
+        <v>232</v>
       </c>
       <c r="X154" s="22" t="n">
-        <v>38</v>
+        <v>161</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
+          <t>고정자산 제각·매각손익</t>
         </is>
       </c>
       <c r="C155" s="22" t="n">
-        <v>-11.374</v>
+        <v>3.07</v>
       </c>
       <c r="E155" s="22" t="n">
-        <v>23.354</v>
+        <v>3.662</v>
       </c>
       <c r="G155" s="22" t="n">
-        <v>410</v>
+        <v>2</v>
       </c>
       <c r="I155" s="22" t="n">
-        <v>516</v>
+        <v>13</v>
       </c>
       <c r="K155" s="22" t="n">
-        <v>-170</v>
+        <v>2</v>
       </c>
       <c r="M155" s="22" t="n">
-        <v>-109</v>
+        <v>5</v>
       </c>
       <c r="S155" s="22" t="n">
-        <v>-314.701</v>
+        <v>2.992</v>
       </c>
       <c r="T155" s="22" t="n">
-        <v>80.486</v>
+        <v>1.431</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>124.479</v>
+        <v>0.433</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>23.354</v>
+        <v>3.662</v>
       </c>
       <c r="W155" s="22" t="n">
-        <v>516</v>
+        <v>13</v>
       </c>
       <c r="X155" s="22" t="n">
-        <v>-109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C156" s="22" t="n">
-        <v>1.05</v>
+        <v>-372.761</v>
       </c>
       <c r="E156" s="22" t="n">
-        <v>-9.332000000000001</v>
+        <v>-93.402</v>
       </c>
       <c r="G156" s="22" t="n">
-        <v>3</v>
+        <v>-174</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="K156" s="22" t="n">
-        <v>24</v>
+        <v>-112</v>
       </c>
       <c r="M156" s="22" t="n">
-        <v>28</v>
+        <v>-240</v>
       </c>
       <c r="S156" s="22" t="n">
-        <v>2.137</v>
+        <v>-251.056</v>
       </c>
       <c r="T156" s="22" t="n">
-        <v>2.737</v>
+        <v>-43.738</v>
       </c>
       <c r="U156" s="22" t="n">
-        <v>-0.571</v>
+        <v>-629.905</v>
       </c>
       <c r="V156" s="22" t="n">
-        <v>-9.332000000000001</v>
+        <v>-93.402</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>28</v>
+        <v>-240</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
-        <v>1382.686</v>
+        <v>26.155</v>
       </c>
       <c r="E157" s="22" t="n">
-        <v>3128.412</v>
+        <v>26.411</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>1038</v>
+        <v>-40</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>1883</v>
+        <v>-59</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>332</v>
+        <v>-36</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>1592</v>
+        <v>59</v>
       </c>
       <c r="S157" s="22" t="n">
-        <v>1986.975</v>
+        <v>-2.921</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>2623.507</v>
+        <v>-1.503</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>2100.709</v>
+        <v>-27.628</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>3128.412</v>
+        <v>26.411</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>1883</v>
+        <v>-59</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>1592</v>
+        <v>59</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="C158" s="22" t="n">
-        <v>0.002</v>
+        <v>0.287</v>
       </c>
       <c r="E158" s="22" t="n">
-        <v>0.003</v>
+        <v>0.623</v>
       </c>
       <c r="G158" s="22" t="n">
         <v>0</v>
@@ -9052,17 +9221,14 @@
       <c r="M158" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S158" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="T158" s="22" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="U158" s="22" t="n">
-        <v>0.002</v>
+        <v>-0.307</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>0.003</v>
+        <v>0.623</v>
       </c>
       <c r="W158" s="22" t="n">
         <v>0</v>
@@ -9074,1008 +9240,1134 @@
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>기타 자산 증감</t>
         </is>
       </c>
       <c r="C159" s="22" t="n">
-        <v>-0.197</v>
+        <v>19.879</v>
       </c>
       <c r="E159" s="22" t="n">
-        <v>-0.366</v>
+        <v>-15.344</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>-0</v>
+        <v>-12</v>
       </c>
       <c r="I159" s="22" t="n">
-        <v>-0</v>
+        <v>-12</v>
       </c>
       <c r="K159" s="22" t="n">
-        <v>-0</v>
+        <v>-9</v>
       </c>
       <c r="M159" s="22" t="n">
-        <v>-6</v>
+        <v>16</v>
       </c>
       <c r="S159" s="22" t="n">
-        <v>-1.166</v>
+        <v>-67.82599999999999</v>
       </c>
       <c r="T159" s="22" t="n">
-        <v>0</v>
+        <v>-31.882</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>-0.24</v>
+        <v>-57.415</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>-0.366</v>
+        <v>-15.344</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>-0</v>
+        <v>-12</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>-6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>리스해약 손실 지급</t>
-        </is>
+          <t>영업채무 증감</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="n">
+        <v>36.037</v>
       </c>
       <c r="E160" s="22" t="n">
-        <v>0</v>
+        <v>-22.342</v>
+      </c>
+      <c r="G160" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>-62</v>
+      </c>
+      <c r="K160" s="22" t="n">
+        <v>-32</v>
+      </c>
+      <c r="M160" s="22" t="n">
+        <v>66</v>
+      </c>
+      <c r="S160" s="22" t="n">
+        <v>331.266</v>
       </c>
       <c r="T160" s="22" t="n">
-        <v>0</v>
+        <v>-84.955</v>
       </c>
       <c r="U160" s="22" t="n">
-        <v>-17.136</v>
+        <v>332.456</v>
       </c>
       <c r="V160" s="22" t="n">
-        <v>0</v>
+        <v>-22.342</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>-62</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
-        </is>
+          <t>미지급 소비세 증감</t>
+        </is>
+      </c>
+      <c r="C161" s="22" t="n">
+        <v>83.214</v>
       </c>
       <c r="E161" s="22" t="n">
-        <v>2.144</v>
+        <v>266.105</v>
+      </c>
+      <c r="G161" s="22" t="n">
+        <v>-118</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="K161" s="22" t="n">
+        <v>27</v>
       </c>
       <c r="M161" s="22" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="S161" s="22" t="n">
-        <v>0</v>
+        <v>-0.331</v>
       </c>
       <c r="T161" s="22" t="n">
-        <v>5.649</v>
+        <v>-99.23999999999999</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>0</v>
+        <v>-50.501</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>2.144</v>
+        <v>266.105</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="X161" s="22" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
-        </is>
+          <t>기타 부채 증감</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="n">
+        <v>-11.374</v>
       </c>
       <c r="E162" s="22" t="n">
-        <v>0</v>
+        <v>23.354</v>
+      </c>
+      <c r="G162" s="22" t="n">
+        <v>410</v>
       </c>
       <c r="I162" s="22" t="n">
-        <v>1</v>
+        <v>516</v>
+      </c>
+      <c r="K162" s="22" t="n">
+        <v>-170</v>
       </c>
       <c r="M162" s="22" t="n">
-        <v>0</v>
+        <v>-109</v>
+      </c>
+      <c r="S162" s="22" t="n">
+        <v>-314.701</v>
+      </c>
+      <c r="T162" s="22" t="n">
+        <v>80.486</v>
+      </c>
+      <c r="U162" s="22" t="n">
+        <v>124.479</v>
       </c>
       <c r="V162" s="22" t="n">
-        <v>0</v>
+        <v>23.354</v>
       </c>
       <c r="W162" s="22" t="n">
-        <v>1</v>
+        <v>516</v>
       </c>
       <c r="X162" s="22" t="n">
-        <v>0</v>
+        <v>-109</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C163" s="22" t="n">
-        <v>20.031</v>
+        <v>1.05</v>
       </c>
       <c r="E163" s="22" t="n">
-        <v>24.981</v>
+        <v>-9.332000000000001</v>
       </c>
       <c r="G163" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I163" s="22" t="n">
         <v>6</v>
       </c>
       <c r="K163" s="22" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="M163" s="22" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="S163" s="22" t="n">
-        <v>98.188</v>
+        <v>2.137</v>
       </c>
       <c r="T163" s="22" t="n">
-        <v>31.77</v>
+        <v>2.737</v>
       </c>
       <c r="U163" s="22" t="n">
-        <v>57.009</v>
+        <v>-0.571</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>24.981</v>
+        <v>-9.332000000000001</v>
       </c>
       <c r="W163" s="22" t="n">
         <v>6</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>보전금 수취</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="n">
+        <v>1382.686</v>
+      </c>
+      <c r="E164" s="22" t="n">
+        <v>3128.412</v>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>1038</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>1883</v>
+      </c>
+      <c r="K164" s="22" t="n">
+        <v>332</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>1592</v>
+      </c>
+      <c r="S164" s="22" t="n">
+        <v>1986.975</v>
       </c>
       <c r="T164" s="22" t="n">
-        <v>0</v>
+        <v>2623.507</v>
       </c>
       <c r="U164" s="22" t="n">
-        <v>17.136</v>
+        <v>2100.709</v>
+      </c>
+      <c r="V164" s="22" t="n">
+        <v>3128.412</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>1883</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>1592</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>보전금 수취</t>
-        </is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="C165" s="22" t="n">
+        <v>0.002</v>
       </c>
       <c r="E165" s="22" t="n">
-        <v>0</v>
+        <v>0.003</v>
+      </c>
+      <c r="G165" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" s="22" t="n">
+        <v>0.001</v>
       </c>
       <c r="U165" s="22" t="n">
-        <v>17.136</v>
+        <v>0.002</v>
       </c>
       <c r="V165" s="22" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="W165" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C166" s="22" t="n">
-        <v>-254.118</v>
+        <v>-0.197</v>
       </c>
       <c r="E166" s="22" t="n">
-        <v>-585.701</v>
+        <v>-0.366</v>
       </c>
       <c r="G166" s="22" t="n">
-        <v>-365</v>
+        <v>-0</v>
       </c>
       <c r="I166" s="22" t="n">
-        <v>-714</v>
+        <v>-0</v>
       </c>
       <c r="K166" s="22" t="n">
-        <v>-86</v>
+        <v>-0</v>
       </c>
       <c r="M166" s="22" t="n">
-        <v>-301</v>
+        <v>-6</v>
       </c>
       <c r="S166" s="22" t="n">
-        <v>-607.545</v>
+        <v>-1.166</v>
       </c>
       <c r="T166" s="22" t="n">
-        <v>-1074.254</v>
+        <v>0</v>
       </c>
       <c r="U166" s="22" t="n">
-        <v>-623.9829999999999</v>
+        <v>-0.24</v>
       </c>
       <c r="V166" s="22" t="n">
-        <v>-585.701</v>
+        <v>-0.366</v>
       </c>
       <c r="W166" s="22" t="n">
-        <v>-714</v>
+        <v>-0</v>
       </c>
       <c r="X166" s="22" t="n">
-        <v>-301</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C167" s="12" t="n">
-        <v>1148.404</v>
-      </c>
-      <c r="E167" s="12" t="n">
-        <v>2569.473</v>
-      </c>
-      <c r="G167" s="12" t="n">
-        <v>677</v>
-      </c>
-      <c r="I167" s="12" t="n">
-        <v>1176</v>
-      </c>
-      <c r="K167" s="12" t="n">
-        <v>251</v>
-      </c>
-      <c r="M167" s="12" t="n">
-        <v>1299</v>
-      </c>
-      <c r="S167" s="12" t="n">
-        <v>1476.453</v>
-      </c>
-      <c r="T167" s="12" t="n">
-        <v>1586.673</v>
-      </c>
-      <c r="U167" s="12" t="n">
-        <v>1533.497</v>
-      </c>
-      <c r="V167" s="12" t="n">
-        <v>2569.473</v>
-      </c>
-      <c r="W167" s="12" t="n">
-        <v>1176</v>
-      </c>
-      <c r="X167" s="12" t="n">
-        <v>1299</v>
+      <c r="A167" s="20" t="inlineStr">
+        <is>
+          <t>리스해약 손실 지급</t>
+        </is>
+      </c>
+      <c r="E167" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" s="22" t="n">
+        <v>-17.136</v>
+      </c>
+      <c r="V167" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="C168" s="22" t="n">
-        <v>-164.014</v>
+          <t>보험금 수취</t>
+        </is>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-360.748</v>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>-69</v>
+        <v>2.144</v>
       </c>
       <c r="I168" s="22" t="n">
-        <v>-234</v>
-      </c>
-      <c r="K168" s="22" t="n">
-        <v>-167</v>
+        <v>0</v>
       </c>
       <c r="M168" s="22" t="n">
-        <v>-211</v>
+        <v>6</v>
       </c>
       <c r="S168" s="22" t="n">
-        <v>-174.167</v>
+        <v>0</v>
       </c>
       <c r="T168" s="22" t="n">
-        <v>-184.843</v>
+        <v>5.649</v>
       </c>
       <c r="U168" s="22" t="n">
-        <v>-218.757</v>
+        <v>0</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>-360.748</v>
+        <v>2.144</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>-234</v>
+        <v>0</v>
       </c>
       <c r="X168" s="22" t="n">
-        <v>-211</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
-        </is>
-      </c>
-      <c r="C169" s="22" t="n">
-        <v>-139.821</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="E169" s="22" t="n">
-        <v>-305.755</v>
-      </c>
-      <c r="G169" s="22" t="n">
-        <v>-127</v>
+        <v>0</v>
       </c>
       <c r="I169" s="22" t="n">
-        <v>-269</v>
-      </c>
-      <c r="K169" s="22" t="n">
-        <v>-74</v>
+        <v>1</v>
       </c>
       <c r="M169" s="22" t="n">
-        <v>-92</v>
-      </c>
-      <c r="S169" s="22" t="n">
-        <v>-31.556</v>
-      </c>
-      <c r="T169" s="22" t="n">
-        <v>-87.977</v>
-      </c>
-      <c r="U169" s="22" t="n">
-        <v>-218.71</v>
+        <v>0</v>
       </c>
       <c r="V169" s="22" t="n">
-        <v>-305.755</v>
+        <v>0</v>
       </c>
       <c r="W169" s="22" t="n">
-        <v>-269</v>
+        <v>1</v>
       </c>
       <c r="X169" s="22" t="n">
-        <v>-92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>보조금 수취</t>
         </is>
       </c>
       <c r="C170" s="22" t="n">
-        <v>-99.999</v>
+        <v>20.031</v>
       </c>
       <c r="E170" s="22" t="n">
-        <v>-99.999</v>
+        <v>24.981</v>
       </c>
       <c r="G170" s="22" t="n">
-        <v>-135</v>
+        <v>5</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>-135</v>
+        <v>6</v>
       </c>
       <c r="K170" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M170" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="S170" s="22" t="n">
+        <v>98.188</v>
       </c>
       <c r="T170" s="22" t="n">
-        <v>0</v>
+        <v>31.77</v>
       </c>
       <c r="U170" s="22" t="n">
-        <v>-168</v>
+        <v>57.009</v>
       </c>
       <c r="V170" s="22" t="n">
-        <v>-99.999</v>
+        <v>24.981</v>
       </c>
       <c r="W170" s="22" t="n">
-        <v>-135</v>
+        <v>6</v>
       </c>
       <c r="X170" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
-      </c>
-      <c r="E171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="22" t="n">
-        <v>243</v>
-      </c>
-      <c r="M171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W171" s="22" t="n">
-        <v>243</v>
-      </c>
-      <c r="X171" s="22" t="n">
-        <v>0</v>
+          <t>보전금 수취</t>
+        </is>
+      </c>
+      <c r="T171" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" s="22" t="n">
+        <v>17.136</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 이행 지출</t>
+          <t>보전금 수취</t>
         </is>
       </c>
       <c r="E172" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G172" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="K172" s="22" t="n">
-        <v>-31</v>
-      </c>
-      <c r="M172" s="22" t="n">
-        <v>-86</v>
+      <c r="U172" s="22" t="n">
+        <v>17.136</v>
       </c>
       <c r="V172" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="W172" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X172" s="22" t="n">
-        <v>-86</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>정기예금 증감</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="C173" s="22" t="n">
-        <v>-1.8</v>
+        <v>-254.118</v>
       </c>
       <c r="E173" s="22" t="n">
-        <v>-3.6</v>
+        <v>-585.701</v>
       </c>
       <c r="G173" s="22" t="n">
-        <v>-1</v>
+        <v>-365</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>1</v>
+        <v>-714</v>
       </c>
       <c r="K173" s="22" t="n">
-        <v>2</v>
+        <v>-86</v>
       </c>
       <c r="M173" s="22" t="n">
-        <v>0</v>
+        <v>-301</v>
+      </c>
+      <c r="S173" s="22" t="n">
+        <v>-607.545</v>
+      </c>
+      <c r="T173" s="22" t="n">
+        <v>-1074.254</v>
       </c>
       <c r="U173" s="22" t="n">
-        <v>0</v>
+        <v>-623.9829999999999</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>-3.6</v>
+        <v>-585.701</v>
       </c>
       <c r="W173" s="22" t="n">
-        <v>1</v>
+        <v>-714</v>
       </c>
       <c r="X173" s="22" t="n">
-        <v>0</v>
+        <v>-301</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="20" t="inlineStr">
-        <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
-      </c>
-      <c r="C174" s="22" t="n">
-        <v>-95.89700000000001</v>
-      </c>
-      <c r="E174" s="22" t="n">
-        <v>-126.666</v>
-      </c>
-      <c r="G174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I174" s="22" t="n">
-        <v>-138</v>
-      </c>
-      <c r="K174" s="22" t="n">
-        <v>-16</v>
-      </c>
-      <c r="M174" s="22" t="n">
-        <v>-24</v>
-      </c>
-      <c r="S174" s="22" t="n">
-        <v>-96.251</v>
-      </c>
-      <c r="T174" s="22" t="n">
-        <v>-94.01300000000001</v>
-      </c>
-      <c r="U174" s="22" t="n">
-        <v>-12.833</v>
-      </c>
-      <c r="V174" s="22" t="n">
-        <v>-126.666</v>
-      </c>
-      <c r="W174" s="22" t="n">
-        <v>-138</v>
-      </c>
-      <c r="X174" s="22" t="n">
-        <v>-24</v>
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="n">
+        <v>1148.404</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>2569.473</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>677</v>
+      </c>
+      <c r="I174" s="12" t="n">
+        <v>1176</v>
+      </c>
+      <c r="K174" s="12" t="n">
+        <v>251</v>
+      </c>
+      <c r="M174" s="12" t="n">
+        <v>1299</v>
+      </c>
+      <c r="S174" s="12" t="n">
+        <v>1476.453</v>
+      </c>
+      <c r="T174" s="12" t="n">
+        <v>1586.673</v>
+      </c>
+      <c r="U174" s="12" t="n">
+        <v>1533.497</v>
+      </c>
+      <c r="V174" s="12" t="n">
+        <v>2569.473</v>
+      </c>
+      <c r="W174" s="12" t="n">
+        <v>1176</v>
+      </c>
+      <c r="X174" s="12" t="n">
+        <v>1299</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C175" s="22" t="n">
-        <v>3.103</v>
+        <v>-164.014</v>
       </c>
       <c r="E175" s="22" t="n">
-        <v>3.377</v>
+        <v>-360.748</v>
       </c>
       <c r="G175" s="22" t="n">
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>58</v>
+        <v>-234</v>
       </c>
       <c r="K175" s="22" t="n">
-        <v>19</v>
+        <v>-167</v>
       </c>
       <c r="M175" s="22" t="n">
-        <v>119</v>
+        <v>-211</v>
       </c>
       <c r="S175" s="22" t="n">
-        <v>0.919</v>
+        <v>-174.167</v>
       </c>
       <c r="T175" s="22" t="n">
-        <v>2.093</v>
+        <v>-184.843</v>
       </c>
       <c r="U175" s="22" t="n">
-        <v>1.293</v>
+        <v>-218.757</v>
       </c>
       <c r="V175" s="22" t="n">
-        <v>3.377</v>
+        <v>-360.748</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>58</v>
+        <v>-234</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>119</v>
+        <v>-211</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득(수입)</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C176" s="22" t="n">
-        <v>0</v>
+        <v>-139.821</v>
       </c>
       <c r="E176" s="22" t="n">
-        <v>0</v>
+        <v>-305.755</v>
+      </c>
+      <c r="G176" s="22" t="n">
+        <v>-127</v>
+      </c>
+      <c r="I176" s="22" t="n">
+        <v>-269</v>
+      </c>
+      <c r="K176" s="22" t="n">
+        <v>-74</v>
+      </c>
+      <c r="M176" s="22" t="n">
+        <v>-92</v>
+      </c>
+      <c r="S176" s="22" t="n">
+        <v>-31.556</v>
       </c>
       <c r="T176" s="22" t="n">
-        <v>0</v>
+        <v>-87.977</v>
       </c>
       <c r="U176" s="22" t="n">
-        <v>6.534</v>
+        <v>-218.71</v>
       </c>
       <c r="V176" s="22" t="n">
-        <v>0</v>
+        <v>-305.755</v>
+      </c>
+      <c r="W176" s="22" t="n">
+        <v>-269</v>
+      </c>
+      <c r="X176" s="22" t="n">
+        <v>-92</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="C177" s="22" t="n">
+        <v>-99.999</v>
+      </c>
+      <c r="E177" s="22" t="n">
+        <v>-99.999</v>
+      </c>
+      <c r="G177" s="22" t="n">
+        <v>-135</v>
       </c>
       <c r="I177" s="22" t="n">
+        <v>-135</v>
+      </c>
+      <c r="K177" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M177" s="22" t="n">
-        <v>-1245</v>
+        <v>0</v>
+      </c>
+      <c r="T177" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" s="22" t="n">
+        <v>-168</v>
+      </c>
+      <c r="V177" s="22" t="n">
+        <v>-99.999</v>
       </c>
       <c r="W177" s="22" t="n">
-        <v>0</v>
+        <v>-135</v>
       </c>
       <c r="X177" s="22" t="n">
-        <v>-1245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C178" s="22" t="n">
-        <v>-0.824</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="E178" s="22" t="n">
-        <v>-0.824</v>
-      </c>
-      <c r="G178" s="22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I178" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K178" s="22" t="n">
-        <v>-1</v>
+        <v>243</v>
       </c>
       <c r="M178" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="S178" s="22" t="n">
-        <v>-1.341</v>
-      </c>
-      <c r="T178" s="22" t="n">
-        <v>-1.526</v>
-      </c>
-      <c r="U178" s="22" t="n">
-        <v>-1.526</v>
+        <v>0</v>
       </c>
       <c r="V178" s="22" t="n">
-        <v>-0.824</v>
+        <v>0</v>
       </c>
       <c r="W178" s="22" t="n">
-        <v>-1</v>
+        <v>243</v>
       </c>
       <c r="X178" s="22" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C179" s="12" t="n">
-        <v>-499.252</v>
-      </c>
-      <c r="E179" s="12" t="n">
-        <v>-894.215</v>
-      </c>
-      <c r="G179" s="12" t="n">
-        <v>-335</v>
-      </c>
-      <c r="I179" s="12" t="n">
-        <v>-479</v>
-      </c>
-      <c r="K179" s="12" t="n">
-        <v>-270</v>
-      </c>
-      <c r="M179" s="12" t="n">
-        <v>-1490</v>
-      </c>
-      <c r="S179" s="12" t="n">
-        <v>-302.396</v>
-      </c>
-      <c r="T179" s="12" t="n">
-        <v>-366.266</v>
-      </c>
-      <c r="U179" s="12" t="n">
-        <v>-611.999</v>
-      </c>
-      <c r="V179" s="12" t="n">
-        <v>-894.215</v>
-      </c>
-      <c r="W179" s="12" t="n">
-        <v>-479</v>
-      </c>
-      <c r="X179" s="12" t="n">
-        <v>-1490</v>
+      <c r="A179" s="20" t="inlineStr">
+        <is>
+          <t>자산복구부채 이행 지출</t>
+        </is>
+      </c>
+      <c r="E179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K179" s="22" t="n">
+        <v>-31</v>
+      </c>
+      <c r="M179" s="22" t="n">
+        <v>-86</v>
+      </c>
+      <c r="V179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X179" s="22" t="n">
+        <v>-86</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>정기예금 증감</t>
         </is>
       </c>
       <c r="C180" s="22" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>-5</v>
+        <v>-3.6</v>
       </c>
       <c r="G180" s="22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I180" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" s="22" t="n">
-        <v>-13.78</v>
-      </c>
-      <c r="T180" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U180" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V180" s="22" t="n">
-        <v>-5</v>
+        <v>-3.6</v>
       </c>
       <c r="W180" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X180" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
-        </is>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="n">
+        <v>-95.89700000000001</v>
       </c>
       <c r="E181" s="22" t="n">
-        <v>0</v>
+        <v>-126.666</v>
+      </c>
+      <c r="G181" s="22" t="n">
+        <v>-0</v>
       </c>
       <c r="I181" s="22" t="n">
-        <v>0</v>
+        <v>-138</v>
+      </c>
+      <c r="K181" s="22" t="n">
+        <v>-16</v>
       </c>
       <c r="M181" s="22" t="n">
-        <v>1300</v>
+        <v>-24</v>
+      </c>
+      <c r="S181" s="22" t="n">
+        <v>-96.251</v>
       </c>
       <c r="T181" s="22" t="n">
-        <v>0</v>
+        <v>-94.01300000000001</v>
       </c>
       <c r="U181" s="22" t="n">
-        <v>27</v>
+        <v>-12.833</v>
       </c>
       <c r="V181" s="22" t="n">
-        <v>0</v>
+        <v>-126.666</v>
       </c>
       <c r="W181" s="22" t="n">
-        <v>0</v>
+        <v>-138</v>
       </c>
       <c r="X181" s="22" t="n">
-        <v>1300</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>임차보증금·보증금 회수</t>
         </is>
       </c>
       <c r="C182" s="22" t="n">
-        <v>-2.388</v>
+        <v>3.103</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>-4.776</v>
+        <v>3.377</v>
       </c>
       <c r="G182" s="22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I182" s="22" t="n">
-        <v>-3</v>
+        <v>58</v>
       </c>
       <c r="K182" s="22" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="M182" s="22" t="n">
-        <v>-2</v>
+        <v>119</v>
       </c>
       <c r="S182" s="22" t="n">
-        <v>-226</v>
+        <v>0.919</v>
       </c>
       <c r="T182" s="22" t="n">
-        <v>0</v>
+        <v>2.093</v>
       </c>
       <c r="U182" s="22" t="n">
-        <v>-28.888</v>
+        <v>1.293</v>
       </c>
       <c r="V182" s="22" t="n">
-        <v>-4.776</v>
+        <v>3.377</v>
       </c>
       <c r="W182" s="22" t="n">
-        <v>-3</v>
+        <v>58</v>
       </c>
       <c r="X182" s="22" t="n">
-        <v>-2</v>
+        <v>119</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="S183" s="22" t="n">
+          <t>연결범위 변경 자회사 주식 취득(수입)</t>
+        </is>
+      </c>
+      <c r="C183" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="22" t="n">
         <v>0</v>
       </c>
       <c r="T183" s="22" t="n">
-        <v>1171.154</v>
+        <v>0</v>
       </c>
       <c r="U183" s="22" t="n">
+        <v>6.534</v>
+      </c>
+      <c r="V183" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 행사에 따른 주식 발행</t>
-        </is>
-      </c>
-      <c r="C184" s="22" t="n">
-        <v>76.494</v>
-      </c>
-      <c r="E184" s="22" t="n">
-        <v>198.55</v>
-      </c>
-      <c r="G184" s="22" t="n">
-        <v>12</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
       </c>
       <c r="I184" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="K184" s="22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M184" s="22" t="n">
-        <v>254</v>
-      </c>
-      <c r="T184" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U184" s="22" t="n">
-        <v>201.894</v>
-      </c>
-      <c r="V184" s="22" t="n">
-        <v>198.55</v>
+        <v>-1245</v>
       </c>
       <c r="W184" s="22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="X184" s="22" t="n">
-        <v>254</v>
+        <v>-1245</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C185" s="22" t="n">
-        <v>0</v>
+        <v>-0.824</v>
       </c>
       <c r="E185" s="22" t="n">
-        <v>0</v>
+        <v>-0.824</v>
       </c>
       <c r="G185" s="22" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="I185" s="22" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="K185" s="22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M185" s="22" t="n">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="S185" s="22" t="n">
+        <v>-1.341</v>
       </c>
       <c r="T185" s="22" t="n">
-        <v>0</v>
+        <v>-1.526</v>
       </c>
       <c r="U185" s="22" t="n">
-        <v>-0.053</v>
+        <v>-1.526</v>
       </c>
       <c r="V185" s="22" t="n">
-        <v>0</v>
+        <v>-0.824</v>
       </c>
       <c r="W185" s="22" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="X185" s="22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="20" t="inlineStr">
-        <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C186" s="22" t="n">
-        <v>-680.458</v>
-      </c>
-      <c r="E186" s="22" t="n">
-        <v>-680.647</v>
-      </c>
-      <c r="G186" s="22" t="n">
-        <v>-746</v>
-      </c>
-      <c r="I186" s="22" t="n">
-        <v>-746</v>
-      </c>
-      <c r="K186" s="22" t="n">
-        <v>-1087</v>
-      </c>
-      <c r="M186" s="22" t="n">
-        <v>-1087</v>
-      </c>
-      <c r="S186" s="22" t="n">
-        <v>-460.8</v>
-      </c>
-      <c r="T186" s="22" t="n">
-        <v>-569.6</v>
-      </c>
-      <c r="U186" s="22" t="n">
-        <v>-643.077</v>
-      </c>
-      <c r="V186" s="22" t="n">
-        <v>-680.647</v>
-      </c>
-      <c r="W186" s="22" t="n">
-        <v>-746</v>
-      </c>
-      <c r="X186" s="22" t="n">
-        <v>-1087</v>
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="n">
+        <v>-499.252</v>
+      </c>
+      <c r="E186" s="12" t="n">
+        <v>-894.215</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>-335</v>
+      </c>
+      <c r="I186" s="12" t="n">
+        <v>-479</v>
+      </c>
+      <c r="K186" s="12" t="n">
+        <v>-270</v>
+      </c>
+      <c r="M186" s="12" t="n">
+        <v>-1490</v>
+      </c>
+      <c r="S186" s="12" t="n">
+        <v>-302.396</v>
+      </c>
+      <c r="T186" s="12" t="n">
+        <v>-366.266</v>
+      </c>
+      <c r="U186" s="12" t="n">
+        <v>-611.999</v>
+      </c>
+      <c r="V186" s="12" t="n">
+        <v>-894.215</v>
+      </c>
+      <c r="W186" s="12" t="n">
+        <v>-479</v>
+      </c>
+      <c r="X186" s="12" t="n">
+        <v>-1490</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 없는 자회사 주식 취득</t>
-        </is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E187" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="S187" s="22" t="n">
-        <v>-18.084</v>
+        <v>-13.78</v>
       </c>
       <c r="T187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V187" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W187" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 발행</t>
-        </is>
-      </c>
-      <c r="S188" s="22" t="n">
-        <v>4.8</v>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="E188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" s="22" t="n">
+        <v>1300</v>
       </c>
       <c r="T188" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="U188" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="V188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X188" s="22" t="n">
+        <v>1300</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
-        </is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="C189" s="22" t="n">
+        <v>-2.388</v>
+      </c>
+      <c r="E189" s="22" t="n">
+        <v>-4.776</v>
+      </c>
+      <c r="G189" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I189" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K189" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M189" s="22" t="n">
+        <v>-2</v>
       </c>
       <c r="S189" s="22" t="n">
-        <v>0</v>
+        <v>-226</v>
       </c>
       <c r="T189" s="22" t="n">
-        <v>-20.861</v>
+        <v>0</v>
+      </c>
+      <c r="U189" s="22" t="n">
+        <v>-28.888</v>
+      </c>
+      <c r="V189" s="22" t="n">
+        <v>-4.776</v>
+      </c>
+      <c r="W189" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X189" s="22" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
-        </is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="S190" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T190" s="22" t="n">
-        <v>-20.861</v>
+        <v>1171.154</v>
       </c>
       <c r="U190" s="22" t="n">
         <v>0</v>
@@ -10084,126 +10376,301 @@
     <row r="191">
       <c r="A191" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>신주예약권 행사에 따른 주식 발행</t>
         </is>
       </c>
       <c r="C191" s="22" t="n">
-        <v>-0.478</v>
+        <v>76.494</v>
       </c>
       <c r="E191" s="22" t="n">
-        <v>-0.98</v>
+        <v>198.55</v>
       </c>
       <c r="G191" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="K191" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="M191" s="22" t="n">
+        <v>254</v>
+      </c>
+      <c r="T191" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" s="22" t="n">
+        <v>201.894</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>198.55</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="22" t="n">
         <v>-0</v>
       </c>
-      <c r="I191" s="22" t="n">
+      <c r="I192" s="22" t="n">
         <v>-0</v>
       </c>
-      <c r="K191" s="22" t="n">
+      <c r="K192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" s="22" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="V192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" s="22" t="n">
         <v>-0</v>
       </c>
-      <c r="M191" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T191" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U191" s="22" t="n">
-        <v>-0.081</v>
-      </c>
-      <c r="V191" s="22" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="W191" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="X191" s="22" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C192" s="12" t="n">
-        <v>-611.83</v>
-      </c>
-      <c r="E192" s="12" t="n">
-        <v>-492.853</v>
-      </c>
-      <c r="G192" s="12" t="n">
-        <v>-736</v>
-      </c>
-      <c r="I192" s="12" t="n">
-        <v>-706</v>
-      </c>
-      <c r="K192" s="12" t="n">
-        <v>-1079</v>
-      </c>
-      <c r="M192" s="12" t="n">
-        <v>463</v>
-      </c>
-      <c r="S192" s="12" t="n">
-        <v>-713.864</v>
-      </c>
-      <c r="T192" s="12" t="n">
-        <v>580.693</v>
-      </c>
-      <c r="U192" s="12" t="n">
-        <v>-438.205</v>
-      </c>
-      <c r="V192" s="12" t="n">
-        <v>-492.853</v>
-      </c>
-      <c r="W192" s="12" t="n">
-        <v>-706</v>
-      </c>
-      <c r="X192" s="12" t="n">
-        <v>463</v>
+      <c r="X192" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="20" t="inlineStr">
         <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C193" s="22" t="n">
+        <v>-680.458</v>
+      </c>
+      <c r="E193" s="22" t="n">
+        <v>-680.647</v>
+      </c>
+      <c r="G193" s="22" t="n">
+        <v>-746</v>
+      </c>
+      <c r="I193" s="22" t="n">
+        <v>-746</v>
+      </c>
+      <c r="K193" s="22" t="n">
+        <v>-1087</v>
+      </c>
+      <c r="M193" s="22" t="n">
+        <v>-1087</v>
+      </c>
+      <c r="S193" s="22" t="n">
+        <v>-460.8</v>
+      </c>
+      <c r="T193" s="22" t="n">
+        <v>-569.6</v>
+      </c>
+      <c r="U193" s="22" t="n">
+        <v>-643.077</v>
+      </c>
+      <c r="V193" s="22" t="n">
+        <v>-680.647</v>
+      </c>
+      <c r="W193" s="22" t="n">
+        <v>-746</v>
+      </c>
+      <c r="X193" s="22" t="n">
+        <v>-1087</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="20" t="inlineStr">
+        <is>
+          <t>연결범위 변경 없는 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="S194" s="22" t="n">
+        <v>-18.084</v>
+      </c>
+      <c r="T194" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="20" t="inlineStr">
+        <is>
+          <t>신주예약권 발행</t>
+        </is>
+      </c>
+      <c r="S195" s="22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T195" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="S196" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" s="22" t="n">
+        <v>-20.861</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="T197" s="22" t="n">
+        <v>-20.861</v>
+      </c>
+      <c r="U197" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C198" s="22" t="n">
+        <v>-0.478</v>
+      </c>
+      <c r="E198" s="22" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="G198" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I198" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K198" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M198" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T198" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" s="22" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="V198" s="22" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="W198" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X198" s="22" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="n">
+        <v>-611.83</v>
+      </c>
+      <c r="E199" s="12" t="n">
+        <v>-492.853</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>-736</v>
+      </c>
+      <c r="I199" s="12" t="n">
+        <v>-706</v>
+      </c>
+      <c r="K199" s="12" t="n">
+        <v>-1079</v>
+      </c>
+      <c r="M199" s="12" t="n">
+        <v>463</v>
+      </c>
+      <c r="S199" s="12" t="n">
+        <v>-713.864</v>
+      </c>
+      <c r="T199" s="12" t="n">
+        <v>580.693</v>
+      </c>
+      <c r="U199" s="12" t="n">
+        <v>-438.205</v>
+      </c>
+      <c r="V199" s="12" t="n">
+        <v>-492.853</v>
+      </c>
+      <c r="W199" s="12" t="n">
+        <v>-706</v>
+      </c>
+      <c r="X199" s="12" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C193" s="22" t="n">
+      <c r="C200" s="22" t="n">
         <v>37.322</v>
       </c>
-      <c r="E193" s="22" t="n">
+      <c r="E200" s="22" t="n">
         <v>1182.405</v>
       </c>
-      <c r="G193" s="22" t="n">
+      <c r="G200" s="22" t="n">
         <v>-393</v>
       </c>
-      <c r="I193" s="22" t="n">
+      <c r="I200" s="22" t="n">
         <v>-10</v>
       </c>
-      <c r="K193" s="22" t="n">
+      <c r="K200" s="22" t="n">
         <v>-1098</v>
       </c>
-      <c r="M193" s="22" t="n">
+      <c r="M200" s="22" t="n">
         <v>271</v>
       </c>
-      <c r="S193" s="22" t="n">
+      <c r="S200" s="22" t="n">
         <v>460.193</v>
       </c>
-      <c r="T193" s="22" t="n">
+      <c r="T200" s="22" t="n">
         <v>1801.1</v>
       </c>
-      <c r="U193" s="22" t="n">
+      <c r="U200" s="22" t="n">
         <v>483.293</v>
       </c>
-      <c r="V193" s="22" t="n">
+      <c r="V200" s="22" t="n">
         <v>1182.405</v>
       </c>
-      <c r="W193" s="22" t="n">
+      <c r="W200" s="22" t="n">
         <v>-10</v>
       </c>
-      <c r="X193" s="22" t="n">
+      <c r="X200" s="22" t="n">
         <v>271</v>
       </c>
     </row>
@@ -10244,7 +10711,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11682,7 +12149,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11734,7 +12201,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11786,7 +12253,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11838,7 +12305,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11890,7 +12357,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11942,7 +12409,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11994,7 +12461,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12004,43 +12471,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -12064,7 +12531,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12116,7 +12583,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12168,7 +12635,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12220,7 +12687,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12272,7 +12739,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12324,7 +12791,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12394,7 +12861,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12446,7 +12913,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12456,49 +12923,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12508,49 +12975,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12560,49 +13027,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12612,43 +13079,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12672,7 +13139,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12724,7 +13191,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12776,7 +13243,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12828,7 +13295,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15080,873 +15547,873 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>비위드 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>컨센서스</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D5" s="54" t="inlineStr">
+      <c r="D5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>2Q 매출</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>93.09</v>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스, 애널리스트 1명</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>fy27 매출</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>380</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>fy27 EPS</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>68.2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>fy27 EPS 90d</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="57" t="n">
         <v>58.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>fy28 매출</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="57" t="n">
         <v>395</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>fy28 EPS</t>
         </is>
       </c>
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="57" t="n">
         <v>76.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>핵심 지표</t>
         </is>
       </c>
-      <c r="B13" s="53" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
+      <c r="B13" s="54" t="n"/>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="A14" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B14" s="54" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D14" s="54" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>omnia licenses 1q</t>
         </is>
       </c>
-      <c r="B15" s="58" t="n">
+      <c r="B15" s="59" t="n">
         <v>5851</v>
       </c>
-      <c r="D15" s="57" t="inlineStr">
+      <c r="D15" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>licenses YoY</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="57" t="n">
         <v>22.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="55" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>arr 1q</t>
         </is>
       </c>
-      <c r="B17" s="56" t="n">
+      <c r="B17" s="57" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>arr YoY</t>
         </is>
       </c>
-      <c r="B18" s="56" t="n">
+      <c r="B18" s="57" t="n">
         <v>37.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>arr fy26end</t>
         </is>
       </c>
-      <c r="B19" s="56" t="n">
+      <c r="B19" s="57" t="n">
         <v>14.7</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>licenses fy26end</t>
         </is>
       </c>
-      <c r="B20" s="58" t="n">
+      <c r="B20" s="59" t="n">
         <v>5721</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>booths 1q</t>
         </is>
       </c>
-      <c r="B21" s="58" t="n">
+      <c r="B21" s="59" t="n">
         <v>6678</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>booths fy26end</t>
         </is>
       </c>
-      <c r="B22" s="58" t="n">
+      <c r="B22" s="59" t="n">
         <v>6660</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="56" t="inlineStr">
         <is>
           <t>sites</t>
         </is>
       </c>
-      <c r="B23" s="58" t="n">
+      <c r="B23" s="59" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="54" t="inlineStr">
         <is>
           <t>radiant</t>
         </is>
       </c>
-      <c r="B25" s="53" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="B25" s="54" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D26" s="54" t="inlineStr">
+      <c r="D26" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>cy25 매출</t>
         </is>
       </c>
-      <c r="B27" s="56" t="n">
+      <c r="B27" s="57" t="n">
         <v>9.4</v>
       </c>
-      <c r="D27" s="57" t="inlineStr">
+      <c r="D27" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>cy25 영업이익</t>
         </is>
       </c>
-      <c r="B28" s="56" t="n">
+      <c r="B28" s="57" t="n">
         <v>2.62</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>cy25 순이익</t>
         </is>
       </c>
-      <c r="B29" s="56" t="n">
+      <c r="B29" s="57" t="n">
         <v>1.95</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="53" t="inlineStr">
+      <c r="A31" s="54" t="inlineStr">
         <is>
           <t>pl 1q</t>
         </is>
       </c>
-      <c r="B31" s="53" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="B31" s="54" t="n"/>
+      <c r="C31" s="54" t="n"/>
+      <c r="D31" s="54" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="54" t="inlineStr">
+      <c r="A32" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B32" s="54" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D32" s="54" t="inlineStr">
+      <c r="D32" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="55" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B33" s="56" t="n">
+      <c r="B33" s="57" t="n">
         <v>94.11</v>
       </c>
-      <c r="D33" s="57" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="55" t="inlineStr">
+      <c r="A34" s="56" t="inlineStr">
         <is>
           <t>cogs</t>
         </is>
       </c>
-      <c r="B34" s="56" t="n">
+      <c r="B34" s="57" t="n">
         <v>79.06</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="55" t="inlineStr">
+      <c r="A35" s="56" t="inlineStr">
         <is>
           <t>gp</t>
         </is>
       </c>
-      <c r="B35" s="56" t="n">
+      <c r="B35" s="57" t="n">
         <v>15.05</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="55" t="inlineStr">
+      <c r="A36" s="56" t="inlineStr">
         <is>
           <t>sga</t>
         </is>
       </c>
-      <c r="B36" s="56" t="n">
+      <c r="B36" s="57" t="n">
         <v>10.25</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="55" t="inlineStr">
+      <c r="A37" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B37" s="56" t="n">
+      <c r="B37" s="57" t="n">
         <v>4.79</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>dep</t>
         </is>
       </c>
-      <c r="B38" s="56" t="n">
+      <c r="B38" s="57" t="n">
         <v>1.18</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>dep 직전</t>
         </is>
       </c>
-      <c r="B39" s="56" t="n">
+      <c r="B39" s="57" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>goodwill</t>
         </is>
       </c>
-      <c r="B40" s="56" t="n">
+      <c r="B40" s="57" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>goodwill 직전</t>
         </is>
       </c>
-      <c r="B41" s="56" t="n">
+      <c r="B41" s="57" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>interest</t>
         </is>
       </c>
-      <c r="B42" s="56" t="n">
+      <c r="B42" s="57" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>pl 1q · 직전</t>
         </is>
       </c>
-      <c r="B44" s="53" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="54" t="inlineStr">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B45" s="54" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D45" s="54" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B46" s="56" t="n">
+      <c r="B46" s="57" t="n">
         <v>89.3</v>
       </c>
-      <c r="D46" s="57" t="inlineStr">
+      <c r="D46" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="55" t="inlineStr">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>cogs</t>
         </is>
       </c>
-      <c r="B47" s="56" t="n">
+      <c r="B47" s="57" t="n">
         <v>77.91</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="55" t="inlineStr">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>gp</t>
         </is>
       </c>
-      <c r="B48" s="56" t="n">
+      <c r="B48" s="57" t="n">
         <v>11.39</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>sga</t>
         </is>
       </c>
-      <c r="B49" s="56" t="n">
+      <c r="B49" s="57" t="n">
         <v>10.05</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="55" t="inlineStr">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B50" s="56" t="n">
+      <c r="B50" s="57" t="n">
         <v>1.34</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="inlineStr">
+      <c r="A52" s="54" t="inlineStr">
         <is>
           <t>bs 1q</t>
         </is>
       </c>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="B52" s="54" t="n"/>
+      <c r="C52" s="54" t="n"/>
+      <c r="D52" s="54" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="54" t="inlineStr">
+      <c r="A53" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B53" s="54" t="inlineStr">
+      <c r="B53" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D53" s="54" t="inlineStr">
+      <c r="D53" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="55" t="inlineStr">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="B54" s="56" t="n">
+      <c r="B54" s="57" t="n">
         <v>45.44</v>
       </c>
-      <c r="D54" s="57" t="inlineStr">
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="55" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>cash fy26end</t>
         </is>
       </c>
-      <c r="B55" s="56" t="n">
+      <c r="B55" s="57" t="n">
         <v>64.92</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="55" t="inlineStr">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>합계 assets</t>
         </is>
       </c>
-      <c r="B56" s="56" t="n">
+      <c r="B56" s="57" t="n">
         <v>142.99</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>net assets</t>
         </is>
       </c>
-      <c r="B57" s="56" t="n">
+      <c r="B57" s="57" t="n">
         <v>80.45</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>dividend paid</t>
         </is>
       </c>
-      <c r="B58" s="56" t="n">
+      <c r="B58" s="57" t="n">
         <v>11.06</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>peers · 9715 트랜스코스모스 (3월 결산, 10/30 발표)</t>
         </is>
       </c>
-      <c r="B60" s="53" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="B60" s="54" t="n"/>
+      <c r="C60" s="54" t="n"/>
+      <c r="D60" s="54" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="54" t="inlineStr">
+      <c r="A61" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B61" s="54" t="inlineStr">
+      <c r="B61" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D61" s="54" t="inlineStr">
+      <c r="D61" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>fc fy27 영업이익</t>
         </is>
       </c>
-      <c r="B62" s="58" t="n">
+      <c r="B62" s="59" t="n">
         <v>168</v>
       </c>
-      <c r="D62" s="57" t="inlineStr">
+      <c r="D62" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="inlineStr">
+      <c r="A63" s="56" t="inlineStr">
         <is>
           <t>fc fy27 EPS</t>
         </is>
       </c>
-      <c r="B63" s="56" t="n">
+      <c r="B63" s="57" t="n">
         <v>360.26</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="55" t="inlineStr">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B64" s="58" t="n">
+      <c r="B64" s="59" t="n">
         <v>3745</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="55" t="inlineStr">
+      <c r="A65" s="56" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="B65" s="56" t="n">
+      <c r="B65" s="57" t="n">
         <v>7.2</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="53" t="inlineStr">
+      <c r="A67" s="54" t="inlineStr">
         <is>
           <t>peers · 4290 프레스티지 인터내셔널 (3월 결산, 10/29 발표)</t>
         </is>
       </c>
-      <c r="B67" s="53" t="n"/>
-      <c r="C67" s="53" t="n"/>
-      <c r="D67" s="53" t="n"/>
+      <c r="B67" s="54" t="n"/>
+      <c r="C67" s="54" t="n"/>
+      <c r="D67" s="54" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="54" t="inlineStr">
+      <c r="A68" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B68" s="54" t="inlineStr">
+      <c r="B68" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D68" s="54" t="inlineStr">
+      <c r="D68" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="55" t="inlineStr">
+      <c r="A69" s="56" t="inlineStr">
         <is>
           <t>fc fy27 EPS</t>
         </is>
       </c>
-      <c r="B69" s="56" t="n">
+      <c r="B69" s="57" t="n">
         <v>47.46</v>
       </c>
-      <c r="D69" s="57" t="inlineStr">
+      <c r="D69" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="55" t="inlineStr">
+      <c r="A70" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B70" s="58" t="n">
+      <c r="B70" s="59" t="n">
         <v>721</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="55" t="inlineStr">
+      <c r="A71" s="56" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="B71" s="56" t="n">
+      <c r="B71" s="57" t="n">
         <v>17.3</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="53" t="inlineStr">
+      <c r="A73" s="54" t="inlineStr">
         <is>
           <t>peers · 6183 벨시스템24 (2월 결산, IFRS)</t>
         </is>
       </c>
-      <c r="B73" s="53" t="n"/>
-      <c r="C73" s="53" t="n"/>
-      <c r="D73" s="53" t="n"/>
+      <c r="B73" s="54" t="n"/>
+      <c r="C73" s="54" t="n"/>
+      <c r="D73" s="54" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="54" t="inlineStr">
+      <c r="A74" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B74" s="54" t="inlineStr">
+      <c r="B74" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D74" s="54" t="inlineStr">
+      <c r="D74" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="55" t="inlineStr">
+      <c r="A75" s="56" t="inlineStr">
         <is>
           <t>fc fy27 EPS</t>
         </is>
       </c>
-      <c r="B75" s="56" t="n">
+      <c r="B75" s="57" t="n">
         <v>114.33</v>
       </c>
-      <c r="D75" s="57" t="inlineStr">
+      <c r="D75" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="A76" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B76" s="58" t="n">
+      <c r="B76" s="59" t="n">
         <v>1374</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="55" t="inlineStr">
+      <c r="A77" s="56" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="B77" s="56" t="n">
+      <c r="B77" s="57" t="n">
         <v>9.1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="inlineStr">
+      <c r="A79" s="54" t="inlineStr">
         <is>
           <t>가이던스 history</t>
         </is>
       </c>
-      <c r="B79" s="53" t="n"/>
-      <c r="C79" s="53" t="n"/>
-      <c r="D79" s="53" t="n"/>
+      <c r="B79" s="54" t="n"/>
+      <c r="C79" s="54" t="n"/>
+      <c r="D79" s="54" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="54" t="inlineStr">
+      <c r="A80" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B80" s="54" t="inlineStr">
+      <c r="B80" s="55" t="inlineStr">
         <is>
           <t>initial 영업이익</t>
         </is>
       </c>
-      <c r="C80" s="54" t="inlineStr">
+      <c r="C80" s="55" t="inlineStr">
         <is>
           <t>실적 영업이익</t>
         </is>
       </c>
-      <c r="D80" s="54" t="inlineStr">
+      <c r="D80" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="55" t="inlineStr">
+      <c r="A81" s="56" t="inlineStr">
         <is>
           <t>FY5/24</t>
         </is>
       </c>
-      <c r="B81" s="56" t="n">
+      <c r="B81" s="57" t="n">
         <v>29</v>
       </c>
-      <c r="C81" s="56" t="n">
+      <c r="C81" s="57" t="n">
         <v>25.43</v>
       </c>
-      <c r="D81" s="57" t="inlineStr">
+      <c r="D81" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="55" t="inlineStr">
+      <c r="A82" s="56" t="inlineStr">
         <is>
           <t>FY5/25</t>
         </is>
       </c>
-      <c r="B82" s="56" t="n">
+      <c r="B82" s="57" t="n">
         <v>32</v>
       </c>
-      <c r="C82" s="56" t="n">
+      <c r="C82" s="57" t="n">
         <v>10.69</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="55" t="inlineStr">
+      <c r="A83" s="56" t="inlineStr">
         <is>
           <t>FY5/26</t>
         </is>
       </c>
-      <c r="B83" s="56" t="n">
+      <c r="B83" s="57" t="n">
         <v>11.5</v>
       </c>
-      <c r="C83" s="56" t="n">
+      <c r="C83" s="57" t="n">
         <v>11.67</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="55" t="inlineStr">
+      <c r="A84" s="56" t="inlineStr">
         <is>
           <t>FY5/27</t>
         </is>
       </c>
-      <c r="B84" s="56" t="n">
+      <c r="B84" s="57" t="n">
         <v>16</v>
       </c>
-      <c r="C84" s="59" t="n"/>
+      <c r="C84" s="60" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15968,24 +16435,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
